--- a/artfynd/A 47260-2022 artfynd.xlsx
+++ b/artfynd/A 47260-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47260-2022 artfynd.xlsx
+++ b/artfynd/A 47260-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17079006</v>
+        <v>17079003</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>765820.2276332139</v>
+        <v>765982</v>
       </c>
       <c r="R2" t="n">
-        <v>7270862.925135758</v>
+        <v>7270754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-07-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -776,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -802,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17079003</v>
+        <v>17079007</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>765982.1313973491</v>
+        <v>765875</v>
       </c>
       <c r="R3" t="n">
-        <v>7270753.981174228</v>
+        <v>7270880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,24 +850,14 @@
           <t>2012-07-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-07-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sparsam/enstaka på platsen, möjlig säker reproduktion</t>
+          <t>allmän på platsen, möjlig säker reproduktion</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +869,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>Gran</t>
@@ -921,6 +891,225 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17079102</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>765989</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7270792</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>allmän på platsen, möjlig säker reproduktion</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Lindberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Lindberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>17079006</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>765820</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7270863</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-07-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-07-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sparsam/enstaka på platsen, möjlig säker reproduktion</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Lindberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Lindberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47260-2022 artfynd.xlsx
+++ b/artfynd/A 47260-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17079003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17079007</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17079102</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,8 +1130,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17079006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>